--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91620</v>
+        <v>91630</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91630</v>
+        <v>91642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91642</v>
+        <v>91643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91643</v>
+        <v>91646</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91646</v>
+        <v>91652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47168-2024 artfynd.xlsx
+++ b/artfynd/A 47168-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254792</v>
       </c>
       <c r="B2" t="n">
-        <v>91652</v>
+        <v>91653</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
